--- a/Blitz-zapis-cold-call-script.xlsx
+++ b/Blitz-zapis-cold-call-script.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Скрипт" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Отработка возражений" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Памятка по продукту" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Кейсы для звонка" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Примеры для звонка" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Скрипт'!$1:$1</definedName>
@@ -503,19 +503,19 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="72" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="78" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="58" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1">
+    <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>СКРИПТ ХОЛОДНОГО ЗВОНКА: «БЛИЦ-ЗАПИСЬ» (ГК ФОРУС)  |  Цель звонка — запись на демонстрацию сервиса (15–20 мин)</t>
+          <t>СКРИПТ ХОЛОДНОГО ЗВОНКА: «БЛИЦ-ЗАПИСЬ» (группа компаний «Форус»)  |  Цель звонка — записать клиента на показ сервиса (15–20 минут)</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -523,17 +523,17 @@
       <c r="D1" s="1" t="n"/>
       <c r="E1" s="1" t="n"/>
     </row>
-    <row r="2">
+    <row r="2" ht="236" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ЛОГИКА ЗВОНКА (не читать клиенту): 70% говорит клиент / 30% менеджер. Сначала доверие к Форус → сбор потребности вопросами → короткое резюме боли → точечная презентация под его ответы → кейс при необходимости → закрытие на демо. Не продаём тариф в холодном звонке — продаём интерес к демонстрации.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+          <t>ЛОГИКА ЗВОНКА (не читать клиенту): большую часть времени говорит клиент, менеджер — меньше. Сначала коротко о «Форус» → вопросы о потребности → коротко повторить боль клиента → рассказать только то, что закрывает его ответы → при необходимости пример внедрения → предложить показ сервиса. В холодном звонке не продаём подписку — договариваемся о показе.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>1. Приветствие + право на разговор</t>
+          <t>1. Приветствие и право на разговор</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -543,51 +543,51 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Добрый день, [ИО]! Меня зовут [имя], компания «Форус». Подскажите, я попал(а) к владельцу / руководителю [салона / автомойки / школы / студии]?</t>
+          <t>Добрый день, [Имя Отчество]! Меня зовут [имя], компания «Форус». Подскажите, я попал(а) к владельцу или руководителю [салона / автомойки / школы / студии]?</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr"/>
       <c r="E3" s="4" t="inlineStr"/>
     </row>
-    <row r="4">
+    <row r="4" ht="60" customHeight="1">
       <c r="A4" s="3" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Если не ЛПР</t>
+          <t>Если это не руководитель</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Подскажите, пожалуйста, с кем лучше обсудить запись клиентов и расписание? Как к нему/ней обратиться и когда удобно перезвонить?</t>
+          <t>Подскажите, пожалуйста, с кем лучше обсудить запись клиентов и расписание? Как к нему или к ней обратиться и когда удобно перезвонить?</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Фиксируем ФИО, роль, время → перезвон</t>
+          <t>Записываем фамилию, имя, отчество, роль и время — затем перезваниваем</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr"/>
     </row>
-    <row r="5">
+    <row r="5" ht="60" customHeight="1">
       <c r="A5" s="3" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Если ЛПР</t>
+          <t>Если это руководитель</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Отлично. У вас буквально 2–3 минуты? Хочу коротко представиться и задать пару вопросов по записи клиентов — без продажи и без обязательств.</t>
+          <t>Отлично. У вас буквально две-три минуты? Хочу коротко представиться и задать пару вопросов по записи клиентов — без продажи и без обязательств.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Ждём «да». Если «нет» — договариваемся о перезвоне с конкретным временем</t>
+          <t>Ждём согласие. Если сейчас некогда — договариваемся о перезвоне с конкретным временем</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr"/>
     </row>
-    <row r="6">
+    <row r="6" ht="60" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>2. Презентация компании «Форус»</t>
@@ -595,31 +595,31 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Говорим (коротко!)</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>«Форус» — группа компаний, более 30 лет в ИТ и автоматизации бизнеса, официальный партнёр 1С. У нас свыше 10 000 клиентов на сопровождении, 18 представительств. Мы сами разрабатываем сервисы под реальные задачи малого бизнеса — один из них как раз «Блиц-запись»: онлайн-запись, расписание и клиентская база в одном окне. Платформа включена в реестр российского ПО.</t>
+          <t>Говорим (очень коротко)</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>«Форус» — крупная компания по автоматизации бизнеса, официальный партнёр фирмы «1С». Мы разработали сервис «Блиц-запись» — для записи клиентов и ведения расписания.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Не растягивать! 2–3 предложения. Сразу к вопросам</t>
+          <t>Не больше двух предложений. Сразу к вопросам</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr"/>
     </row>
-    <row r="7">
+    <row r="7" ht="44" customHeight="1">
       <c r="A7" s="3" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Мостик к вопросам</t>
+          <t>Переход к вопросам</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Чтобы понять, актуально ли вам это вообще, расскажите, пожалуйста, как у вас сейчас устроена запись клиентов?</t>
+          <t>Чтобы понять, актуально ли вам это, расскажите, пожалуйста: как у вас сейчас устроена запись клиентов?</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr"/>
     </row>
-    <row r="8">
+    <row r="8" ht="44" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>3. Сбор потребности (клиент говорит больше менеджера)</t>
@@ -642,7 +642,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>БАЗОВЫЙ БЛОК (всем сегментам: салоны, автомойки, курсы, студии, ИП)</t>
+          <t>ОСНОВНОЙ БЛОК (для всех: салоны, автомойки, курсы, студии, индивидуальные предприниматели)</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="55" customHeight="1">
+    <row r="9" ht="60" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>3.1 Как записывают сейчас</t>
@@ -669,12 +669,12 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>[ИО], как сейчас клиенты к вам записываются — звонок, мессенджеры, соцсети, или уже есть онлайн-запись?</t>
+          <t>[Имя Отчество], как сейчас клиенты к вам записываются — звонок, сообщения в мессенджерах, социальные сети, или уже есть запись через интернет?</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Через какой канал чаще всего приходят записи — Instagram, WhatsApp, звонок администратору?</t>
+          <t>Через какой канал чаще всего приходят записи — социальные сети, мессенджер или звонок администратору?</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -683,7 +683,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="55" customHeight="1">
+    <row r="10" ht="44" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>3.2 Кто ведёт расписание</t>
@@ -696,52 +696,52 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Кто у вас отвечает за расписание и запись — вы сами, администратор или мастер/сотрудник?</t>
+          <t>Кто у вас отвечает за расписание и запись — вы сами, администратор или мастер / сотрудник?</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Сколько мастеров одновременно работают в смене? Кто разруливает накладки по времени?</t>
+          <t>Сколько мастеров одновременно работают в смене? Кто решает накладки по времени?</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Автомойка: сколько постов и кто диспетчеризирует поток? Курсы: кто ведёт расписание преподавателей?</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="55" customHeight="1">
+          <t>Автомойка: сколько постов и кто распределяет поток? Курсы: кто ведёт расписание преподавателей?</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="76" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>3.3 Инструмент (если есть)</t>
+          <t>3.3 Чем пользуются сейчас</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Закрытый → открытый</t>
+          <t>Закрытый, затем открытый</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Вы сейчас чем-то пользуетесь для записи — тетрадь, Excel, YCLIENTS, DIKIDI, что-то ещё?
-→ Если назвали сервис: А что в нём удобно, а что бесит или кажется лишним?</t>
+          <t>Вы сейчас чем-то пользуетесь для записи — тетрадь, таблица, «Юклиентс», «Дикиди» или что-то ещё?
+Если назвали сервис: а что в нём удобно, а что мешает или кажется лишним?</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Стоимость текущего сервиса зависит от числа мастеров? Это для вас критично?</t>
+          <t>Стоимость текущего сервиса зависит от числа мастеров? Это для вас важно?</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Автомойка: текущий сервис умеет нормально работать с постами и пиковой нагрузкой? Курсы: есть запись на группы/индивидуальные?</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="55" customHeight="1">
+          <t>Автомойка: текущий сервис нормально работает с постами и пиковой нагрузкой? Курсы: есть запись на группы и на индивидуальные занятия?</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>3.4 Потери и хаос</t>
+          <t>3.4 Потери и путаница</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Бывает, что клиент не может дозвониться в пик, пишет в WhatsApp — и запись «теряется»? Расскажите, как часто такое случается.</t>
+          <t>Бывает, что клиент не может дозвониться в час пик, пишет в мессенджер — и запись «теряется»? Расскажите, как часто такое случается.</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -765,7 +765,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="55" customHeight="1">
+    <row r="13" ht="44" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>3.5 Неявки</t>
@@ -773,13 +773,13 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Закрытый → открытый</t>
+          <t>Закрытый, затем открытый</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Вы отправляете клиентам напоминания перед визитом?
-→ Если нет: А неявки / «забыл» насколько бьют по загрузке?</t>
+Если нет: а неявки и «забыл прийти» насколько бьют по загрузке?</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -793,10 +793,10 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="55" customHeight="1">
+    <row r="14" ht="44" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>3.6 Запись вне часов</t>
+          <t>3.6 Запись вне рабочих часов</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -806,21 +806,21 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Клиенты часто пишут/звонят вечером или в выходные, когда администратора нет на месте?</t>
+          <t>Клиенты часто пишут или звонят вечером и в выходные, когда администратора нет на месте?</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Хотели бы, чтобы клиент сам выбирал мастера и время ночью/утром без вашего участия?</t>
+          <t>Хотели бы, чтобы клиент сам выбирал мастера и время ночью или утром без вашего участия?</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Автомойка: готовы принимать онлайн-запись 24/7, чтобы не терять заявки ночью?</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="55" customHeight="1">
+          <t>Автомойка: готовы принимать запись через интернет круглосуточно, чтобы не терять заявки ночью?</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="44" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
           <t>3.7 База клиентов</t>
@@ -843,14 +843,14 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Насколько важно видеть историю авто / услуг / посещений по каждому клиенту?</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="55" customHeight="1">
+          <t>Насколько важно видеть историю автомобиля, услуг и посещений по каждому клиенту?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="44" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>3.8 Боль №1 (ключевой)</t>
+          <t>3.8 Главная боль</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Что бы вы изменили в записи клиентов в первую очередь, если бы можно было махнуть волшебной палочкой?</t>
+          <t>Что бы вы изменили в записи клиентов в первую очередь, если можно было бы сделать это легко?</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -874,10 +874,10 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="55" customHeight="1">
+    <row r="17" ht="44" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>3.9 Приоритет / срочность</t>
+          <t>3.9 Насколько тема сейчас важна</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -901,10 +901,10 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="60" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>3.10 Резюме потребности (обязательно!)</t>
+          <t>3.10 Повторить потребность (обязательно)</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -919,15 +919,15 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Ждём подтверждение. Только после «да» переходим к презентации — говорим про то, что откликнулось, а не «всё подряд»</t>
+          <t>Ждём подтверждение. Только после согласия переходим к рассказу о сервисе — говорим про то, что откликнулось, а не «всё подряд»</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
     </row>
-    <row r="19">
+    <row r="19" ht="60" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>4. Презентация «Блиц-запись» (коротко, под боль)</t>
+          <t>4. Рассказ о «Блиц-записи» (коротко, под боль)</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -937,13 +937,13 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Называем 2–3 пункта, которые закрывают ЕГО ответы. Не читаем прайс. Не спорим с текущим сервисом — предлагаем сравнить на демо.</t>
+          <t>Называем два-три пункта, которые закрывают ответы клиента. Не читаем прайс. Не спорим с текущим сервисом — предлагаем сравнить на показе.</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr"/>
       <c r="E19" s="4" t="inlineStr"/>
     </row>
-    <row r="20" ht="60" customHeight="1">
+    <row r="20" ht="76" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Если теряют заявки / много звонков</t>
@@ -956,7 +956,7 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>«Блиц-запись» как раз про это: клиент сам записывается онлайн 24/7 — с сайта, соцсетей, карт. Заявка сразу попадает в календарь администратора, без накладок. Меньше пропущенных звонков — меньше потерянных клиентов.</t>
+          <t>«Блиц-запись» как раз про это: клиент сам записывается через интернет в любое время — с сайта, из социальных сетей, с карт. Заявка сразу попадает в календарь администратора, без накладок. Меньше пропущенных звонков — меньше потерянных клиентов.</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr"/>
@@ -965,7 +965,7 @@
     <row r="21" ht="60" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Если хаос в расписании / накладки</t>
+          <t>Если путаница в расписании / накладки</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Всё расписание — в одном рабочем месте администратора: по сотрудникам, кабинетам, постам. Система резервирует слот и не даёт задвоить запись. Загрузку видно сразу.</t>
+          <t>Всё расписание — в одном рабочем месте администратора: по сотрудникам, кабинетам, постам. Система занимает время и не даёт задвоить запись. Загрузку видно сразу.</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr"/>
@@ -994,7 +994,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Сервис сам отправляет напоминания перед визитом (SMS/мессенджеры). На практике это снижает простои из‑за неявок — по нашим данным, до ~31%.</t>
+          <t>Сервис сам отправляет напоминания перед визитом — смс или сообщения в мессенджерах. На практике это снижает простои из‑за неявок — по нашим данным, примерно на треть.</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr"/>
@@ -1019,10 +1019,10 @@
       <c r="D23" s="4" t="inlineStr"/>
       <c r="E23" s="4" t="inlineStr"/>
     </row>
-    <row r="24" ht="60" customHeight="1">
+    <row r="24" ht="92" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Если дорого / избыточный функционал (YCLIENTS и др.)</t>
+          <t>Если дорого / слишком много лишних функций</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1032,16 +1032,16 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>У «Блиц-записи» цена не растёт от числа мастеров/сотрудников — платите за сервис, а не «за голову». Многое из «тяжёлых» систем малому бизнесу просто не нужно. Плюс при переходе с другого сервиса даём до 6 месяцев в подарок, а перенос базы берём на себя.</t>
+          <t>У «Блиц-записи» цена не растёт от числа мастеров и сотрудников — платите за сервис, а не «за каждого человека». Многое из больших систем малому бизнесу просто не нужно. Плюс при переходе с другого сервиса даём до шести месяцев в подарок, а перенос базы берём на себя.</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr"/>
       <c r="E24" s="4" t="inlineStr"/>
     </row>
-    <row r="25" ht="60" customHeight="1">
+    <row r="25" ht="92" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Общий каркас (если нужно одним абзацем)</t>
+          <t>Общий рассказ (если нужен один абзац)</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1051,16 +1051,16 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>«Блиц-запись» — наша разработка (ГК «Форус»): онлайн-запись, расписание, база клиентов, напоминания и аналитика загрузки в одном окне. Работает с компьютера, планшета и телефона без установки. Мы помогаем подключить, настроить услуги, сотрудников и виджеты — вы не остаётесь один на один с системой.</t>
+          <t>«Блиц-запись» — наша разработка: запись клиентов через интернет, расписание, база клиентов, напоминания и анализ загрузки в одном окне. Работает с компьютера, планшета и телефона без установки программ. Мы помогаем подключить, настроить услуги, сотрудников и ссылки на запись — вы не остаётесь один на один с системой.</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr"/>
       <c r="E25" s="4" t="inlineStr"/>
     </row>
-    <row r="26">
+    <row r="26" ht="44" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>5. Социальное доказательство (1 кейс — по сегменту)</t>
+          <t>5. Пример внедрения (один — по сегменту)</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1070,16 +1070,16 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Только если клиент сомневается или спрашивает «а у кого уже стоит?» — не впихивать в каждый звонок.</t>
+          <t>Только если клиент сомневается или спрашивает «а у кого уже стоит?» — не вставлять в каждый звонок.</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr"/>
       <c r="E26" s="4" t="inlineStr"/>
     </row>
-    <row r="27">
+    <row r="27" ht="92" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Кейс «Луна» (салон)</t>
+          <t>Пример «Луна» (салон)</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -1089,16 +1089,16 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Салон красоты «Луна» ушёл с YCLIENTS на «Блиц-запись»: перенесли ~2000 клиентов и ~100 услуг под ключ. Годовая стоимость снизилась примерно на 37% (с 36 360 ₽ до 22 800 ₽), плюс 6 месяцев в подарок за переход. Через полтора месяца оформили годовую подписку.</t>
+          <t>Салон красоты «Луна» перешёл с «Юклиентс» на «Блиц-запись»: мы перенесли около двух тысяч клиентов и около ста услуг. Годовая стоимость снизилась примерно на треть — с 36 360 рублей до 22 800 рублей, плюс шесть месяцев в подарок за переход. Через полтора месяца салон оформил годовую подписку.</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr"/>
       <c r="E27" s="4" t="inlineStr"/>
     </row>
-    <row r="28">
+    <row r="28" ht="92" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Кейс «Элис» (автомойка)</t>
+          <t>Пример «Элис» (автомойка)</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -1108,16 +1108,16 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Автомоечный комплекс «Элис» в Иркутске (8 постов, ~2000 записей в месяц) тоже ушёл с YCLIENTS. Сделали под них удобный календарь, «цифровую тетрадку» для пиковых часов, модуль зарплат и подключили кассу. Базу перенесли без потери контактов, дали 6 месяцев в подарок — и они остались на годовой подписке.</t>
+          <t>Автомоечный комплекс «Элис» в Иркутске — восемь постов, около двух тысяч записей в месяц — тоже ушёл с «Юклиентс». Сделали под них удобный календарь, быструю запись администратором в час пик, расчёт зарплат и подключили кассу. Базу перенесли без потери контактов, дали шесть месяцев в подарок — и они остались на годовой подписке.</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr"/>
       <c r="E28" s="4" t="inlineStr"/>
     </row>
-    <row r="29">
+    <row r="29" ht="76" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>6. Закрытие на ДЕМО (главное ЦЕЛЕВОЕ действие)</t>
+          <t>6. Предложить показ сервиса (главная цель звонка)</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -1127,20 +1127,20 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Давайте не на словах — покажу за 15–20 минут, как это выглядит именно под ваш формат: календарь, онлайн-запись, напоминания. Вы просто оцените, заходит или нет. Когда удобнее: завтра до обеда или после?[вариант B: вторник / среда]</t>
+          <t>Давайте не на словах — покажу за 15–20 минут, как это выглядит именно под ваш формат: календарь, запись через интернет, напоминания. Вы просто оцените, подходит или нет. Когда удобнее: завтра до обеда или после? Или во вторник / в среду?</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Всегда даём выбор из двух слотов (альтернативный закрытие). Не спрашиваем «вам интересно?» — спрашиваем «когда удобно»</t>
+          <t>Всегда даём выбор из двух вариантов времени. Не спрашиваем «вам интересно?» — спрашиваем «когда удобно»</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr"/>
     </row>
-    <row r="30">
+    <row r="30" ht="76" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Если «надо подумать»</t>
+          <t>Если говорит «надо подумать»</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
@@ -1150,16 +1150,16 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Конечно. Как раз поэтому и предлагаю короткую демонстрацию — без оплаты и без обязательств, просто посмотрите интерфейс. После демо будет понятнее, думать есть о чём. Давайте поставим 15 минут на [день] — и вы спокойно примете решение?</t>
+          <t>Конечно. Как раз поэтому и предлагаю короткий показ — без оплаты и без обязательств, просто посмотрите, как устроена система. После показа будет понятнее, есть ли о чём думать. Давайте поставим 15 минут на [день] — и вы спокойно примете решение?</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr"/>
       <c r="E30" s="4" t="inlineStr"/>
     </row>
-    <row r="31">
+    <row r="31" ht="76" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Фиксация договорённости</t>
+          <t>Закрепить договорённость</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -1169,20 +1169,20 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Отлично. На какую почту / в какой мессенджер отправить ссылку и напоминание? Подтвердим: [дата], [время], демонстрация «Блиц-запись», около 15–20 минут. Я за день и за час напомню. Хорошего дня, [ИО]!</t>
+          <t>Отлично. На какую почту или в какой мессенджер отправить ссылку и напоминание? Подтвердим: [дата], [время], показ «Блиц-запись», около 15–20 минут. Я за день и за час напомню. Хорошего дня, [Имя Отчество]!</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>После звонка: письмо со ссылкой + задача в CRM (см. регламент после записи на демо)</t>
+          <t>После звонка: письмо со ссылкой и задача в системе учёта клиентов (см. регламент после записи на показ)</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr"/>
     </row>
-    <row r="32">
+    <row r="32" ht="60" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>7. Если демо сейчас не ставят</t>
+          <t>7. Если показ сейчас не ставят</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -1192,20 +1192,20 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Хорошо, не давлю. Тогда зафиксирую ваш запрос: [боль]. Могу направить короткое КП на почту и созвониться [день/время] — сравним с тем, как у вас сейчас. Какая почта удобнее?</t>
+          <t>Хорошо, не давлю. Тогда зафиксирую ваш запрос: [боль]. Могу направить короткое коммерческое предложение на почту и созвониться [день / время] — сравним с тем, как у вас сейчас. Какая почта удобнее?</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Мини-следующий шаг обязателен: письмо / перезвон / материал. Звонок без next step = потерянный лид</t>
+          <t>Следующий шаг обязателен: письмо, перезвон или материал. Звонок без следующего шага — потерянный контакт</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr"/>
     </row>
-    <row r="34">
+    <row r="34" ht="188" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>ПАМЯТКА МЕНЕДЖЕРУ: не продавать тариф на холодном; не спорить с YCLIENTS/DIKIDI — звать сравнить на демо; не монологировать дольше 40–50 сек подряд; после каждого блока вопросов — пауза и слушание; цифры тарифа — только если спросил сам (см. лист «Памятка по продукту»).</t>
+          <t>ПАМЯТКА МЕНЕДЖЕРУ: не продавать тариф в холодном звонке; не спорить с «Юклиентс» и «Дикиди» — звать сравнить на показе; не говорить дольше 40–50 секунд подряд; после каждого блока вопросов — пауза и слушание; цифры тарифа — только если клиент спросил сам (см. лист «Памятка по продукту»).</t>
         </is>
       </c>
     </row>
@@ -1226,23 +1226,23 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="88" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ОТРАБОТКА ВОЗРАЖЕНИЙ — «БЛИЦ-ЗАПИСЬ» (микро/малый бизнес, ИП: салоны, автомойки, курсы, студии)</t>
+          <t>ОТРАБОТКА ВОЗРАЖЕНИЙ — «БЛИЦ-ЗАПИСЬ» (микро- и малый бизнес, индивидуальные предприниматели: салоны, автомойки, курсы, студии)</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
       <c r="C1" s="1" t="n"/>
     </row>
-    <row r="2">
+    <row r="2" ht="24" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Возражение</t>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="70" customHeight="1">
+    <row r="3" ht="60" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Мне некогда / занят</t>
@@ -1267,16 +1267,16 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Понимаю, поэтому и не отнимаю много времени. Предлагаю 15 минут демонстрации в удобный слот — вы просто посмотрите, есть ли смысл возвращаться к теме. Когда спокойнее: утро или вечер?</t>
+          <t>Понимаю, поэтому и не отнимаю много времени. Предлагаю 15 минут показа в удобное время — вы просто посмотрите, есть ли смысл возвращаться к теме. Когда спокойнее: утро или вечер?</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Свести к конкретному слоту демо</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
+          <t>Договориться о конкретном времени показа</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="76" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Нас всё устраивает / и так нормально</t>
@@ -1284,33 +1284,33 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Отлично, значит процесс уже выстроен — это сильная сторона. Часто смотрят «Блиц» не потому что «всё плохо», а чтобы убрать лишние звонки администратору и не терять записи вечером/в выходные. Давайте за 15 минут сравните с тем, как у вас сейчас — вдруг окажется полезным запасным вариантом?</t>
+          <t>Отлично, значит процесс уже выстроен — это сильная сторона. Часто смотрят «Блиц» не потому что «всё плохо», а чтобы убрать лишние звонки администратору и не терять записи вечером и в выходные. Давайте за 15 минут сравните с тем, как у вас сейчас — вдруг окажется полезным запасным вариантом?</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Снять защиту «нас всё ок» → любопытство</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="70" customHeight="1">
+          <t>Снять защиту «нас всё устраивает» и вызвать интерес</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="92" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>У нас уже есть YCLIENTS / DIKIDI / другой сервис</t>
+          <t>У нас уже есть «Юклиентс» / «Дикиди» / другой сервис</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Значит, ценность онлайн-записи вы уже понимаете — это хорошо. Клиенты часто уходят к нам из‑за цены «за мастера», перегруженного интерфейса или слабой поддержки под их задачи. Салон «Луна» и мойка «Элис» как раз переехали с YCLIENTS: базу перенесли мы, плюс до 6 месяцев в подарок за переход. Предлагаю коротко показать разницу на демо — без обязательств.</t>
+          <t>Значит, ценность записи через интернет вы уже понимаете — это хорошо. Клиенты часто приходят к нам из‑за цены «за мастера», перегруженного экрана или слабой поддержки под их задачи. Салон «Луна» и мойка «Элис» как раз переехали с «Юклиентс»: базу перенесли мы, плюс до шести месяцев в подарок за переход. Предлагаю коротко показать разницу — без обязательств.</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Рефрейм: не «бросить», а «сравнить»</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="70" customHeight="1">
+          <t>Не уговаривать «бросить» сервис, а предложить сравнить</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="92" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Это дорого</t>
@@ -1318,50 +1318,50 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Давайте опираться на цифры. Базовый ориентир — от 1 500 ₽/мес при оплате на 2 года, при оплате на год — около 1 900 ₽/мес; цена не растёт от числа мастеров. Для сравнения: салон «Луна» экономит порядка 13 500 ₽ в год относительно прежнего сервиса. На демо посчитаем относительно вашей текущей схемы — часто выходит дешевле «привычного».</t>
+          <t>Давайте опираться на цифры. Ориентир — от 1 500 рублей в месяц при оплате на два года, при оплате на год — около 1 900 рублей в месяц; цена не растёт от числа мастеров. Для сравнения: салон «Луна» экономит порядка 13 500 рублей в год относительно прежнего сервиса. На показе посчитаем относительно вашей текущей схемы — часто выходит дешевле привычного.</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Перевести из эмоции в сравнение на демо</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="70" customHeight="1">
+          <t>Перевести разговор из эмоции в сравнение на показе</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="76" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>У нас маленький бизнес / я один (ИП, 1–2 мастера)</t>
+          <t>У нас маленький бизнес / я один (индивидуальный предприниматель, 1–2 мастера)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Как раз для микробизнеса сервис и делали простым: запись, календарь, база, напоминания — без лишних модулей «для сетей». Есть вариант с оплатой по факту онлайн-записей (баланс от 1 000 ₽) — удобно, если поток небольшой. На демо покажем именно «лёгкий» сценарий под вас.</t>
+          <t>Как раз для небольшого бизнеса сервис и делали простым: запись, календарь, база, напоминания — без лишних блоков «для сетей». Есть вариант с оплатой по факту записей через интернет (баланс от 1 000 рублей) — удобно, если поток небольшой. На показе покажем именно простой сценарий под вас.</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Снять страх «это для крупных»</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="70" customHeight="1">
+          <t>Убрать страх «это только для крупных»</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="92" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Клиенты всё равно звонят / не будут пользоваться онлайн</t>
+          <t>Клиенты всё равно звонят / не будут пользоваться записью через интернет</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Часть клиентов всегда будет звонить — и это нормально. Задача сервиса — забрать тех, кто готов записаться сам (вечером, с работы, из соцсети), и разгрузить администратора. По практике больше 40% записей может приходить через онлайн. Администраторская запись при этом никуда не девается.</t>
+          <t>Часть клиентов всегда будет звонить — и это нормально. Задача сервиса — забрать тех, кто готов записаться сам (вечером, с работы, из социальной сети), и разгрузить администратора. По практике больше 40% записей может приходить через интернет. Запись через администратора при этом никуда не девается.</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>И «онлайн», и запись админом — вместе</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="70" customHeight="1">
+          <t>Показать, что оба способа записи работают вместе</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Боимся переносить базу / потерять клиентов</t>
@@ -1369,16 +1369,16 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Переход берём на себя: в кейсах переносили тысячи контактов и услуги под ключ, бизнес не останавливали. Тестовый период есть — сначала смотрите и проверяете, оплату принимаете когда готовы.</t>
+          <t>Переход берём на себя: в примерах внедрения переносили тысячи контактов и услуги целиком, бизнес не останавливали. Пробный период есть — сначала смотрите и проверяете, оплату принимаете, когда готовы.</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Снять страх миграции</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="70" customHeight="1">
+          <t>Снять страх переноса данных</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="76" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Не хотим ничего внедрять / сложно</t>
@@ -1386,33 +1386,33 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Мы подключаем и настраиваем услуги, расписание, сотрудников и ссылки на запись сами. Вам не нужно разбираться «с нуля». На демо как раз увидите, сколько действий займёт день администратора — обычно это проще тетради и чатов.</t>
+          <t>Мы подключаем и настраиваем услуги, расписание, сотрудников и ссылки на запись сами. Вам не нужно разбираться «с нуля». На показе как раз увидите, сколько действий займёт день администратора — обычно это проще тетради и переписки в чатах.</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Экспертиза Форус = сопровождение</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="70" customHeight="1">
+          <t>Показать, что сопровождение берёт на себя «Форус»</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="76" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Пришлите на почту / в WhatsApp</t>
+          <t>Пришлите на почту / в мессенджер</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Конечно, направлю короткое КП. Чтобы материал был в точку, уточню один момент: что сейчас больнее — пропущенные заявки, неявки или цена текущего сервиса? … Спасибо. И давайте сразу поставим 15 минут на просмотр — так КП не потеряется в почте. Когда удобно?</t>
+          <t>Конечно, направлю короткое коммерческое предложение. Чтобы материал был в точку, уточню один момент: что сейчас больнее — пропущенные заявки, неявки или цена текущего сервиса? … Спасибо. И давайте сразу поставим 15 минут на просмотр — так предложение не потеряется в почте. Когда удобно?</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Не отпустить только в «пришлите»</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="70" customHeight="1">
+          <t>Не оставлять разговор только на «пришлите»</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Надо посоветоваться с партнёром / администратором</t>
@@ -1420,50 +1420,50 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Логично. Давайте пригласим его/её сразу на демонстрацию — за те же 15–20 минут оба увидите систему и быстрее примете решение. Когда вам обоим удобно?</t>
+          <t>Логично. Давайте пригласим его или её сразу на показ — за те же 15–20 минут оба увидите систему и быстрее примете решение. Когда вам обоим удобно?</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Демо с ЛПР+влияющим</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="70" customHeight="1">
+          <t>Пригласить на показ и руководителя, и того, кто влияет на решение</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="92" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Работаем в тетради / Excel — нам хватает</t>
+          <t>Работаем в тетради / таблице — нам хватает</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Тетрадь понятна и привычна. Обычно ломается в пик: накладки, потерянные сообщения в WhatsApp, нет напоминаний. «Блиц» не усложняет жизнь — это тот же журнал, только цифровой, плюс онлайн-запись и напоминания. Посмотрите 15 минут — если тетрадь реально удобнее, честно останетесь на ней.</t>
+          <t>Тетрадь понятна и привычна. Обычно ломается в час пик: накладки, потерянные сообщения в мессенджере, нет напоминаний. «Блиц» не усложняет жизнь — это тот же журнал, только в цифровом виде, плюс запись через интернет и напоминания. Посмотрите 15 минут — если тетрадь реально удобнее, честно останетесь на ней.</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Уважение к привычке + демо</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="70" customHeight="1">
+          <t>Уважение к привычке и приглашение на показ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Нет сайта — онлайн-запись не нужна</t>
+          <t>Нет сайта — запись через интернет не нужна</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Сайт не обязателен. Виджет и ссылку на запись ставят в WhatsApp, соцсети, на карты — клиент переходит по ссылке и выбирает время. Многие ИП начинают именно так.</t>
+          <t>Сайт не обязателен. Ссылку на запись ставят в мессенджер, социальные сети, на карты — клиент переходит по ссылке и выбирает время. Многие индивидуальные предприниматели начинают именно так.</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Снять ложный барьер «нужен сайт»</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="70" customHeight="1">
+          <t>Убрать ложный барьер «нужен сайт»</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="76" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Не доверяем новым сервисам / кто вы такие</t>
@@ -1471,16 +1471,16 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>«Блиц-запись» — разработка группы компаний «Форус»: более 30 лет на рынке, официальный партнёр 1С, продукт в реестре российского ПО. Рядом поддержка и сопровождение внедрения, не «коробка без ответа». На демо покажем живой кабинет и кейсы таких же салонов и моек.</t>
+          <t>«Блиц-запись» — разработка группы компаний «Форус»: более 30 лет на рынке, официальный партнёр фирмы «1С», продукт в реестре российского программного обеспечения. Рядом поддержка и помощь при запуске, не «коробка без ответа». На показе покажем живой кабинет и примеры таких же салонов и моек.</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Доверие к бренду Форус</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="70" customHeight="1">
+          <t>Укрепить доверие к «Форус»</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Сейчас не сезон / потом</t>
@@ -1488,29 +1488,29 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Как раз вне пика удобнее спокойно настроить запись и базу, чтобы к сезону уже принимать заявки 24/7. Давайте поставим короткий слот на этой неделе — потом будет сложнее выкроить время.</t>
+          <t>Как раз вне пика удобнее спокойно настроить запись и базу, чтобы к сезону уже принимать заявки круглосуточно. Давайте поставим короткое время на этой неделе — потом будет сложнее выкроить время.</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Срочность через подготовку к сезону</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="70" customHeight="1">
+          <t>Создать срочность через подготовку к сезону</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="76" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>А какая цена? (вопрос-возражение)</t>
+          <t>А какая цена?</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Ориентир: 2 500 ₽/мес при коротком сроке; при оплате на год — около 1 900 ₽/мес, на 2 года — от 1 500 ₽/мес. Точную схему лучше показать на демо вместе с вашим сценарием (кол-во сотрудников, есть ли уже сервис). Могу забронировать 15 минут — и сразу посчитаем.</t>
+          <t>Ориентир: 2 500 рублей в месяц при коротком сроке; при оплате на год — около 1 900 рублей в месяц, на два года — от 1 500 рублей в месяц. Точную схему лучше показать на встрече вместе с вашим сценарием: сколько сотрудников, есть ли уже сервис. Могу забронировать 15 минут — и сразу посчитаем.</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Цена → демо, не торг в холоде</t>
+          <t>От цены — к показу, без торга в холодном звонке</t>
         </is>
       </c>
     </row>
@@ -1529,21 +1529,21 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ПАМЯТКА МЕНЕДЖЕРУ — «БЛИЦ-ЗАПИСЬ» (для подготовки к звонку, клиенту не читать целиком)</t>
+          <t>ПАМЯТКА МЕНЕДЖЕРУ — «БЛИЦ-ЗАПИСЬ» (для подготовки к звонку; клиенту не читать целиком)</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
     </row>
-    <row r="2">
+    <row r="2" ht="24" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Тема</t>
@@ -1555,7 +1555,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="48" customHeight="1">
+    <row r="3" ht="60" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Продукт</t>
@@ -1563,11 +1563,11 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>«Блиц-запись» — многофункциональный сервис для управления записями клиентов, расписанием, клиентской базой и загрузкой сотрудников в одном рабочем пространстве. Разработка НПФ «Форус».</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="48" customHeight="1">
+          <t>«Блиц-запись» — сервис для управления записями клиентов, расписанием, клиентской базой и загрузкой сотрудников в одном рабочем пространстве. Разработка научно-производственной фирмы «Форус».</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Для кого</t>
@@ -1575,11 +1575,11 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Салоны красоты и барбершопы; автомойки и мойки самообслуживания; медицинские/стоматологические клиники; образовательные центры и курсы; фитнес и спортстудии; частные специалисты; любой бизнес по предварительной записи.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="48" customHeight="1">
+          <t>Салоны красоты и барбершопы; автомойки и мойки самообслуживания; медицинские и стоматологические клиники; образовательные центры и курсы; фитнес и спортивные студии; частные специалисты; любой бизнес по предварительной записи.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Сегмент звонка</t>
@@ -1587,47 +1587,47 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Микро и малый бизнес, ИП.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="48" customHeight="1">
+          <t>Микро- и малый бизнес, индивидуальные предприниматели.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>УТП</t>
+          <t>Сильные стороны</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Простая запись + расписание + база; цена не от числа мастеров; сопровождение внедрения Форус; переход с других сервисов под ключ; до 6 мес. в подарок при миграции; реестр российского ПО.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="48" customHeight="1">
+          <t>Простая запись, расписание и база; цена не зависит от числа мастеров; сопровождение внедрения от «Форус»; переход с других сервисов целиком; до шести месяцев в подарок при переходе; реестр российского программного обеспечения.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="76" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Ключевые функции</t>
+          <t>Основные возможности</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Онлайн-запись 24/7; единое место администратора; управление загрузкой (сотрудники/кабинеты/посты); напоминания; клиентская база и история; аналитика загрузки; роли и доступы; интеграции (телефония, CRM, касса, 1С, мессенджеры и др.); доступ из браузера без установки.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="48" customHeight="1">
+          <t>Запись через интернет круглосуточно; единое место администратора; управление загрузкой (сотрудники, кабинеты, посты); напоминания; клиентская база и история; анализ загрузки; роли и доступы; связь с телефонией, программой учёта клиентов, кассой, «1С», мессенджерами; доступ из браузера без установки программ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Цифры с сайта/КП</t>
+          <t>Цифры с сайта и коммерческого предложения</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>&gt;40% записей через онлайн; &gt;19% записей за первые 14 дней; на 31% меньше простоев из‑за неявок; 64% автовладельцев выбирают онлайн-запись (опрос FIT Service / Gruzdev-Analyze, 2024).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="48" customHeight="1">
+          <t>Больше 40% записей через интернет; больше 19% записей за первые 14 дней; примерно на 31% меньше простоев из‑за неявок; 64% автовладельцев выбирают запись через интернет (опрос 2024 года).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="76" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Тарифы (ориентир)</t>
@@ -1635,35 +1635,35 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>3 мес — 2 500 ₽/мес; 6 мес — 2 300 ₽/мес; 1 год — 1 900 ₽/мес; 2 года — 1 500 ₽/мес. Спец.offer: оплата за факт онлайн-записей (баланс от 1 000 ₽). При переходе с другого сервиса — до +6 месяцев.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="48" customHeight="1">
+          <t>3 месяца — 2 500 рублей в месяц; 6 месяцев — 2 300 рублей в месяц; 1 год — 1 900 рублей в месяц; 2 года — 1 500 рублей в месяц. Есть вариант оплаты за фактические записи через интернет (баланс от 1 000 рублей). При переходе с другого сервиса — до шести месяцев дополнительно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="44" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Триал</t>
+          <t>Пробный период</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>14 дней бесплатно / тестовый доступ (озвучивать как возможность «потрогать» после демо).</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="48" customHeight="1">
+          <t>14 дней бесплатно / тестовый доступ (озвучивать как возможность «потрогать» после показа).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>ЦЕЛЬ холодного звонка</t>
+          <t>Цель холодного звонка</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Запись на демонстрацию сервиса 15–20 минут (не продажа подписки в звонке).</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="48" customHeight="1">
+          <t>Записать клиента на показ сервиса на 15–20 минут (не продавать подписку в звонке).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Контакты продукта</t>
@@ -1671,55 +1671,55 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>+7 992 117-29-16 · vmoskvitina@forus.ru · blitz@forus.ru · сайт блиц-запись.рф · Форус: forus.ru, +7 (3952) 78-00-00</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="48" customHeight="1">
+          <t>+7 992 117-29-16 · vmoskvitina@forus.ru · blitz@forus.ru · сайт блиц-запись.рф · «Форус»: forus.ru, +7 (3952) 78-00-00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Кейс «Луна»</t>
+          <t>Пример «Луна»</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Салон красоты, переход с YCLIENTS. ~2000 клиентов, 6 мастеров, ~100 услуг. Экономия ~37% (36 360 → 22 800 ₽/год) + 6 мес. в подарок. Оплата годовой подписки 07.08.2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="48" customHeight="1">
+          <t>Салон красоты, переход с «Юклиентс». Около 2000 клиентов, 6 мастеров, около 100 услуг. Экономия около 37% (с 36 360 до 22 800 рублей в год) плюс шесть месяцев в подарок. Оплата годовой подписки 07.08.2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Кейс «Элис»</t>
+          <t>Пример «Элис»</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Автомоечный комплекс, 8 постов, ~2000 записей/мес. Переход с YCLIENTS. Кастом: календарь, «цифровая тетрадка», зарплаты, ККТ. +6 мес. в подарок. Годовая подписка с 04.2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="48" customHeight="1">
+          <t>Автомоечный комплекс, 8 постов, около 2000 записей в месяц. Переход с «Юклиентс». Под клиента: календарь, быстрая запись администратором, зарплаты, касса. Плюс шесть месяцев в подарок. Годовая подписка с апреля 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="44" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>После записи на демо</t>
+          <t>После записи на показ</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Письмо со ссылкой → напоминание за день → за час → менеджер на встрече → ОС в течение 3 дней (см. регламент в репозитории).</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="48" customHeight="1">
+          <t>Письмо со ссылкой → напоминание за день → за час → менеджер на встрече → обратная связь в течение трёх дней (см. регламент в репозитории).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="44" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Чего НЕ делать</t>
+          <t>Чего не делать</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Не читать весь функционал; не спорить с конкурентами; не давить тарифом; не заканчивать звонок без next step; не говорить больше клиента.</t>
+          <t>Не читать весь функционал; не спорить с конкурентами; не давить тарифом; не заканчивать звонок без следующего шага; не говорить больше клиента.</t>
         </is>
       </c>
     </row>
@@ -1738,28 +1738,28 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ШПАРГАЛКА ПО КЕЙСАМ — коротко вставить в разговор</t>
+          <t>ШПАРГАЛКА ПО ПРИМЕРАМ ВНЕДРЕНИЯ — коротко вставить в разговор</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
       <c r="C1" s="1" t="n"/>
       <c r="D1" s="1" t="n"/>
     </row>
-    <row r="2">
+    <row r="2" ht="24" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Кейс</t>
+          <t>Пример</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>Боль до</t>
+          <t>Боль до перехода</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
@@ -1778,7 +1778,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="80" customHeight="1">
+    <row r="3" ht="60" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Салон «Луна»</t>
@@ -1791,19 +1791,19 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>YCLIENTS дорого (цена от числа мастеров), лишний функционал, медленная загрузка</t>
+          <t>«Юклиентс» дорого (цена от числа мастеров), лишний функционал, медленная загрузка</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>«Перенесли 2000 клиентов под ключ, экономия около 37% в год, +6 месяцев за переход. Салон остался на годовой подписке.»</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="80" customHeight="1">
+          <t>«Перенесли две тысячи клиентов целиком, экономия около трети в год, плюс шесть месяцев за переход. Салон остался на годовой подписке.»</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>АК «Элис»</t>
+          <t>Комплекс «Элис»</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -1813,19 +1813,19 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Дорого (~120 тыс. ₽/год), ошибки в зарплатах, отказ конкурента по телефонии, тяжёлый интерфейс</t>
+          <t>Дорого (около 120 тысяч рублей в год), ошибки в зарплатах, отказ конкурента по телефонии, тяжёлый интерфейс</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>«Сделали календарь под 8 постов, «цифровую тетрадку» для пика, зарплаты и кассу. Базу сохранили. +6 месяцев в подарок.»</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
+          <t>«Сделали календарь под восемь постов, быструю запись для часа пик, зарплаты и кассу. Базу сохранили. Плюс шесть месяцев в подарок.»</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Как вставлять: 1) клиент назвал конкурента → кейс перехода; 2) боится миграции → «перенос под ключ»; 3) жалуется на цену → цифры «Луны»; 4) автобизнес/посты → «Элис». Один кейс за звонок достаточно.</t>
+          <t>Как вставлять: 1) клиент назвал конкурента — пример перехода; 2) боится переноса данных — «перенос берём на себя»; 3) жалуется на цену — цифры «Луны»; 4) автобизнес и посты — «Элис». Одного примера за звонок достаточно.</t>
         </is>
       </c>
     </row>

--- a/Blitz-zapis-cold-call-script.xlsx
+++ b/Blitz-zapis-cold-call-script.xlsx
@@ -12,9 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Памятка по продукту" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Примеры для звонка" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Скрипт'!$1:$1</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -505,17 +503,17 @@
   <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="78" customWidth="1" min="3" max="3"/>
-    <col width="58" customWidth="1" min="4" max="4"/>
-    <col width="58" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="4" max="4"/>
+    <col width="56" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>СКРИПТ ХОЛОДНОГО ЗВОНКА: «БЛИЦ-ЗАПИСЬ» (группа компаний «Форус»)  |  Цель звонка — записать клиента на показ сервиса (15–20 минут)</t>
+          <t>СКРИПТ ХОЛОДНОГО ЗВОНКА: «БЛИЦ-ЗАПИСЬ»  |  Цель — записать клиента на демонстрацию сервиса (15–20 минут)</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -523,17 +521,17 @@
       <c r="D1" s="1" t="n"/>
       <c r="E1" s="1" t="n"/>
     </row>
-    <row r="2" ht="236" customHeight="1">
+    <row r="2" ht="204" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ЛОГИКА ЗВОНКА (не читать клиенту): большую часть времени говорит клиент, менеджер — меньше. Сначала коротко о «Форус» → вопросы о потребности → коротко повторить боль клиента → рассказать только то, что закрывает его ответы → при необходимости пример внедрения → предложить показ сервиса. В холодном звонке не продаём подписку — договариваемся о показе.</t>
+          <t>Как идёт звонок (для себя, клиенту не читать): сначала знакомимся и коротко говорим, кто мы → задаём вопросы и слушаем → своими словами повторяем, что услышали → рассказываем только то, что откликнулось клиенту → если нужно, приводим пример → приглашаем на демонстрацию. В звонке не продаём тариф — договариваемся о встрече.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="60" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>1. Приветствие и право на разговор</t>
+          <t>1. Первичный контакт / приветствие и презентация компании</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -541,9 +539,9 @@
           <t>Говорим</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Добрый день, [Имя Отчество]! Меня зовут [имя], компания «Форус». Подскажите, я попал(а) к владельцу или руководителю [салона / автомойки / школы / студии]?</t>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Добрый день, [Имя Отчество]! Меня зовут [имя], компания «Форус». Я попал(а) к владельцу или руководителю [салона / автомойки / школы / студии]?</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr"/>
@@ -553,64 +551,60 @@
       <c r="A4" s="3" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Если это не руководитель</t>
+          <t>Если это не ЛПР</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Подскажите, пожалуйста, с кем лучше обсудить запись клиентов и расписание? Как к нему или к ней обратиться и когда удобно перезвонить?</t>
+          <t>Подскажите, пожалуйста, с кем лучше поговорить про запись клиентов и расписание? Как к человеку обратиться и когда удобнее перезвонить?</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Записываем фамилию, имя, отчество, роль и время — затем перезваниваем</t>
+          <t>Записываем ФИО, роль и время — перезваниваем</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr"/>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="44" customHeight="1">
       <c r="A5" s="3" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Если это руководитель</t>
+          <t>Если это ЛПР</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Отлично. У вас буквально две-три минуты? Хочу коротко представиться и задать пару вопросов по записи клиентов — без продажи и без обязательств.</t>
+          <t>Скажите, у вас есть две-три минуты? Хочу коротко рассказать, кто мы, и уточнить, как у вас сейчас устроена запись клиентов.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Ждём согласие. Если сейчас некогда — договариваемся о перезвоне с конкретным временем</t>
+          <t>Если сейчас некогда — договариваемся о перезвоне с конкретным временем</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr"/>
     </row>
     <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>2. Презентация компании «Форус»</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Говорим (очень коротко)</t>
+      <c r="A6" s="3" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Презентация компании</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>«Форус» — крупная компания по автоматизации бизнеса, официальный партнёр фирмы «1С». Мы разработали сервис «Блиц-запись» — для записи клиентов и ведения расписания.</t>
+          <t>Наша компания занимается автоматизацией записи клиентов и предлагает для этого удобный сервис — «Блиц-запись». Мы из группы компаний «Форус», работаем с бизнесом в сфере услуг.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Не больше двух предложений. Сразу к вопросам</t>
+          <t>Два предложения — и сразу к вопросам. Не растягивать</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr"/>
     </row>
-    <row r="7" ht="44" customHeight="1">
+    <row r="7" ht="28" customHeight="1">
       <c r="A7" s="3" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
@@ -619,12 +613,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Чтобы понять, актуально ли вам это, расскажите, пожалуйста: как у вас сейчас устроена запись клиентов?</t>
+          <t>Расскажите, пожалуйста, как у вас сейчас записываются клиенты?</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Открытый вопрос — клиент начинает говорить</t>
+          <t>Открытый вопрос — дальше говорит клиент</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr"/>
@@ -632,7 +626,7 @@
     <row r="8" ht="44" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>3. Сбор потребности (клиент говорит больше менеджера)</t>
+          <t>2. Сбор потребности (больше говорит клиент)</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -642,7 +636,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>ОСНОВНОЙ БЛОК (для всех: салоны, автомойки, курсы, студии, индивидуальные предприниматели)</t>
+          <t>ОСНОВНЫЕ ВОПРОСЫ (салоны, автомойки, курсы, студии, ИП)</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -659,7 +653,7 @@
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>3.1 Как записывают сейчас</t>
+          <t>2.1 Как записывают сейчас</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -669,12 +663,12 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>[Имя Отчество], как сейчас клиенты к вам записываются — звонок, сообщения в мессенджерах, социальные сети, или уже есть запись через интернет?</t>
+          <t>Клиенты к вам чаще звонят, пишут в мессенджеры, приходят из соцсетей — или уже есть запись через интернет?</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Через какой канал чаще всего приходят записи — социальные сети, мессенджер или звонок администратору?</t>
+          <t>Через что чаще всего записываются — соцсети, мессенджер или звонок администратору?</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -683,10 +677,10 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="44" customHeight="1">
+    <row r="10" ht="60" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>3.2 Кто ведёт расписание</t>
+          <t>2.2 Кто ведёт расписание</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -696,52 +690,52 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Кто у вас отвечает за расписание и запись — вы сами, администратор или мастер / сотрудник?</t>
+          <t>А кто у вас этим занимается — вы сами, администратор или мастер?</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Сколько мастеров одновременно работают в смене? Кто решает накладки по времени?</t>
+          <t>Сколько мастеров в смене? Кто разруливает, если времена пересеклись?</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Автомойка: сколько постов и кто распределяет поток? Курсы: кто ведёт расписание преподавателей?</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="76" customHeight="1">
+          <t>Автомойка: сколько постов и кто распределяет машины? Курсы: кто ведёт расписание преподавателей?</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>3.3 Чем пользуются сейчас</t>
+          <t>2.3 Чем пользуются сейчас</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Закрытый, затем открытый</t>
+          <t>Закрытый → открытый</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Вы сейчас чем-то пользуетесь для записи — тетрадь, таблица, «Юклиентс», «Дикиди» или что-то ещё?
-Если назвали сервис: а что в нём удобно, а что мешает или кажется лишним?</t>
+          <t>Вы сейчас чем-то пользуетесь для записи — тетрадью, таблицей, «Юклиентс», «Дикиди» или чем-то ещё?
+Если назвали сервис: а что в нём нравится, а что раздражает?</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Стоимость текущего сервиса зависит от числа мастеров? Это для вас важно?</t>
+          <t>Стоимость вашего сервиса зависит от числа мастеров? Это для вас ощутимо?</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Автомойка: текущий сервис нормально работает с постами и пиковой нагрузкой? Курсы: есть запись на группы и на индивидуальные занятия?</t>
+          <t>Автомойка: удобно ли в текущем сервисе работать с постами в час пик? Курсы: можно ли записывать и на группы, и на индивидуальные занятия?</t>
         </is>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>3.4 Потери и путаница</t>
+          <t>2.4 Где теряются клиенты</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -751,52 +745,52 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Бывает, что клиент не может дозвониться в час пик, пишет в мессенджер — и запись «теряется»? Расскажите, как часто такое случается.</t>
+          <t>Бывает такое, что в час пик клиент не может дозвониться, пишет в мессенджер — и запись куда-то пропадает? Как часто так случается?</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Бывают ли двойные записи на одного мастера или «окна», которые сложно закрыть?</t>
+          <t>Бывают ли двойные записи на одного мастера или «дыры» в расписании, которые сложно закрыть?</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Автомойка: что происходит в часы пик — очередь, путаница по постам? Курсы: как часто ученики забывают про занятие?</t>
+          <t>Автомойка: что происходит в час пик — очередь, путаница по постам? Курсы: часто ли ученики забывают про занятие?</t>
         </is>
       </c>
     </row>
     <row r="13" ht="44" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>3.5 Неявки</t>
+          <t>2.5 Неявки</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Закрытый, затем открытый</t>
+          <t>Закрытый → открытый</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Вы отправляете клиентам напоминания перед визитом?
-Если нет: а неявки и «забыл прийти» насколько бьют по загрузке?</t>
+          <t>Вы напоминаете клиентам о визите заранее?
+Если нет: а неявки сильно бьют по загрузке?</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Какой примерно процент неявок без предупреждения?</t>
+          <t>Какой примерно процент людей не приходит без предупреждения?</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Автомойка: неявки оставляют простой поста? Курсы: как отрабатываете пропуски?</t>
+          <t>Автомойка: из-за неявок пост простаивает? Курсы: как отрабатываете пропуски?</t>
         </is>
       </c>
     </row>
     <row r="14" ht="44" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>3.6 Запись вне рабочих часов</t>
+          <t>2.6 Запись вечером и в выходные</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -806,24 +800,24 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Клиенты часто пишут или звонят вечером и в выходные, когда администратора нет на месте?</t>
+          <t>Клиенты часто пишут или звонят вечером и в выходные, когда администратора уже нет?</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Хотели бы, чтобы клиент сам выбирал мастера и время ночью или утром без вашего участия?</t>
+          <t>Было бы удобно, если бы клиент сам выбирал мастера и время, даже когда вас нет на месте?</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Автомойка: готовы принимать запись через интернет круглосуточно, чтобы не терять заявки ночью?</t>
+          <t>Автомойка: принимали бы заявки круглосуточно, чтобы ночные обращения не терялись?</t>
         </is>
       </c>
     </row>
     <row r="15" ht="44" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>3.7 База клиентов</t>
+          <t>2.7 База клиентов</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -833,24 +827,24 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Где сейчас хранится база клиентов и история визитов — в телефоне, тетради, сервисе?</t>
+          <t>А база клиентов и история визитов у вас где хранится — в телефоне, в тетради, в сервисе?</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Можете ли быстро понять, кто из клиентов давно не был, и вернуть его?</t>
+          <t>Можете быстро понять, кто давно не был, и напомнить о себе?</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Насколько важно видеть историю автомобиля, услуг и посещений по каждому клиенту?</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="44" customHeight="1">
+          <t>Насколько важно видеть историю по клиенту — услуги, визиты, для мойки ещё и по автомобилю?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>3.8 Главная боль</t>
+          <t>2.8 Что больше всего мешает</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -860,24 +854,24 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Если взять запись и расписание — что сейчас отнимает больше всего времени или нервов?</t>
+          <t>Если честно: что в записи и расписании сейчас больше всего отнимает время или нервы?</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Что бы вы изменили в записи клиентов в первую очередь, если можно было бы сделать это легко?</t>
+          <t>Если бы можно было поменять одну вещь в записи клиентов — что бы это было?</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Что для вас важнее: меньше звонков администратору, меньше простоев или контроль загрузки?</t>
+          <t>Что для вас важнее: меньше звонков администратору, меньше простоев или чтобы загрузку было видно?</t>
         </is>
       </c>
     </row>
     <row r="17" ht="44" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>3.9 Насколько тема сейчас важна</t>
+          <t>2.9 Насколько тема сейчас живая</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -887,24 +881,24 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Эту тему сейчас вообще смотрите, или «болит», но руки не доходят?</t>
+          <t>Вы эту тему сейчас как-то смотрите, или она есть, но руки не доходят?</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Готовы ли рассмотреть замену текущего сервиса, если по деньгам и простоте будет выгоднее?</t>
+          <t>Если найдётся вариант проще и выгоднее текущего — готовы сравнить?</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Если покажем за 15 минут, как это работает у похожих бизнесов — интересно посмотреть?</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="60" customHeight="1">
+          <t>Если за 15 минут покажем, как это устроено у похожих бизнесов — интересно будет посмотреть?</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="44" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>3.10 Повторить потребность (обязательно)</t>
+          <t>2.10 Повторяем, что услышали</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -914,20 +908,20 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Правильно ли я понял(а): сейчас у вас [как записывают], главная сложность — [боль клиента], и важно [что хочет получить]. Верно?</t>
+          <t>Правильно понимаю: сейчас у вас [как записывают], больше всего мешает [боль клиента], и важно [что хочет получить]. Верно?</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Ждём подтверждение. Только после согласия переходим к рассказу о сервисе — говорим про то, что откликнулось, а не «всё подряд»</t>
+          <t>Ждём «да». Дальше говорим только про то, что откликнулось — не про весь сервис сразу</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
     </row>
-    <row r="19" ht="60" customHeight="1">
+    <row r="19" ht="44" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>4. Рассказ о «Блиц-записи» (коротко, под боль)</t>
+          <t>3. Рассказ о «Блиц-записи» (коротко, под боль клиента)</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -937,7 +931,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Называем два-три пункта, которые закрывают ответы клиента. Не читаем прайс. Не спорим с текущим сервисом — предлагаем сравнить на показе.</t>
+          <t>Берём два-три пункта из ответов клиента. Прайс не читаем. С текущим сервисом не спорим — предлагаем посмотреть на демонстрации.</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr"/>
@@ -946,17 +940,17 @@
     <row r="20" ht="76" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Если теряют заявки / много звонков</t>
+          <t>Если теряют заявки или много звонков</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Связка</t>
+          <t>Говорим</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>«Блиц-запись» как раз про это: клиент сам записывается через интернет в любое время — с сайта, из социальных сетей, с карт. Заявка сразу попадает в календарь администратора, без накладок. Меньше пропущенных звонков — меньше потерянных клиентов.</t>
+          <t>Как раз для этого и делали «Блиц-запись»: клиент сам записывается через интернет — с сайта, из соцсетей, с карт. Заявка сразу падает в календарь администратора, без накладок. Меньше пропущенных звонков — меньше потерянных клиентов.</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr"/>
@@ -965,17 +959,17 @@
     <row r="21" ht="60" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Если путаница в расписании / накладки</t>
+          <t>Если путаница в расписании</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Связка</t>
+          <t>Говорим</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Всё расписание — в одном рабочем месте администратора: по сотрудникам, кабинетам, постам. Система занимает время и не даёт задвоить запись. Загрузку видно сразу.</t>
+          <t>Всё расписание в одном месте: по сотрудникам, кабинетам, постам. Система не даёт записать двух клиентов на одно и то же время. Загрузку видно сразу.</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr"/>
@@ -984,64 +978,64 @@
     <row r="22" ht="60" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Если неявки / забывают</t>
+          <t>Если неявки и «забыл прийти»</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Связка</t>
+          <t>Говорим</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Сервис сам отправляет напоминания перед визитом — смс или сообщения в мессенджерах. На практике это снижает простои из‑за неявок — по нашим данным, примерно на треть.</t>
+          <t>Сервис сам напоминает клиенту о визите — смс или сообщение в мессенджере. По нашему опыту, простоев из‑за неявок становится заметно меньше — примерно на треть.</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr"/>
       <c r="E22" s="4" t="inlineStr"/>
     </row>
-    <row r="23" ht="60" customHeight="1">
+    <row r="23" ht="44" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Если база размазана / нет возвратов</t>
+          <t>Если база размазана</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Связка</t>
+          <t>Говорим</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Внутри — полноценная клиентская база: контакты, история визитов, комментарии. Удобно возвращать клиентов и видеть, с кем давно не общались.</t>
+          <t>Внутри есть клиентская база: контакты, история визитов, комментарии. Можно быстро найти, кто давно не был, и вернуть человека.</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr"/>
       <c r="E23" s="4" t="inlineStr"/>
     </row>
-    <row r="24" ht="92" customHeight="1">
+    <row r="24" ht="76" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Если дорого / слишком много лишних функций</t>
+          <t>Если дорого или слишком много лишнего</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Связка</t>
+          <t>Говорим</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>У «Блиц-записи» цена не растёт от числа мастеров и сотрудников — платите за сервис, а не «за каждого человека». Многое из больших систем малому бизнесу просто не нужно. Плюс при переходе с другого сервиса даём до шести месяцев в подарок, а перенос базы берём на себя.</t>
+          <t>У нас цена не растёт от числа мастеров — платите за сервис, а не «за каждого человека». Многое из больших систем малому бизнесу просто не нужно. Если переходите с другого сервиса — даём до шести месяцев в подарок, базу переносим сами.</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr"/>
       <c r="E24" s="4" t="inlineStr"/>
     </row>
-    <row r="25" ht="92" customHeight="1">
+    <row r="25" ht="76" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Общий рассказ (если нужен один абзац)</t>
+          <t>Если нужен общий рассказ</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1051,7 +1045,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>«Блиц-запись» — наша разработка: запись клиентов через интернет, расписание, база клиентов, напоминания и анализ загрузки в одном окне. Работает с компьютера, планшета и телефона без установки программ. Мы помогаем подключить, настроить услуги, сотрудников и ссылки на запись — вы не остаётесь один на один с системой.</t>
+          <t>«Блиц-запись» — это запись клиентов через интернет, расписание, база и напоминания в одном окне. Работает с компьютера, планшета и телефона, ничего ставить не нужно. Мы помогаем подключить и настроить — услуги, сотрудников, ссылки на запись.</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr"/>
@@ -1060,7 +1054,7 @@
     <row r="26" ht="44" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>5. Пример внедрения (один — по сегменту)</t>
+          <t>4. Пример внедрения (по сегменту, если нужно)</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1070,7 +1064,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Только если клиент сомневается или спрашивает «а у кого уже стоит?» — не вставлять в каждый звонок.</t>
+          <t>Только если клиент сомневается или спрашивает «а у кого это уже стоит». В каждый звонок не вставляем.</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr"/>
@@ -1079,7 +1073,7 @@
     <row r="27" ht="92" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Пример «Луна» (салон)</t>
+          <t>Салон «Луна»</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -1089,7 +1083,7 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Салон красоты «Луна» перешёл с «Юклиентс» на «Блиц-запись»: мы перенесли около двух тысяч клиентов и около ста услуг. Годовая стоимость снизилась примерно на треть — с 36 360 рублей до 22 800 рублей, плюс шесть месяцев в подарок за переход. Через полтора месяца салон оформил годовую подписку.</t>
+          <t>Салон красоты «Луна» ушёл с «Юклиентс» к нам. Мы перенесли около двух тысяч клиентов и около ста услуг. За год они стали платить примерно на треть меньше — было 36 360 рублей, стало 22 800, плюс шесть месяцев в подарок за переход. Через полтора месяца оформили годовую подписку.</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr"/>
@@ -1098,7 +1092,7 @@
     <row r="28" ht="92" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Пример «Элис» (автомойка)</t>
+          <t>Автомойка «Элис»</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -1108,7 +1102,7 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Автомоечный комплекс «Элис» в Иркутске — восемь постов, около двух тысяч записей в месяц — тоже ушёл с «Юклиентс». Сделали под них удобный календарь, быструю запись администратором в час пик, расчёт зарплат и подключили кассу. Базу перенесли без потери контактов, дали шесть месяцев в подарок — и они остались на годовой подписке.</t>
+          <t>Автомоечный комплекс «Элис» в Иркутске — восемь постов, около двух тысяч записей в месяц — тоже ушёл с «Юклиентс». Сделали им удобный календарь, быструю запись для часа пик, расчёт зарплат, подключили кассу. Базу перенесли без потерь, дали шесть месяцев в подарок — и они остались на годе.</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr"/>
@@ -1117,7 +1111,7 @@
     <row r="29" ht="76" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>6. Предложить показ сервиса (главная цель звонка)</t>
+          <t>5. Приглашение на демонстрацию (главная цель звонка)</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -1127,17 +1121,17 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Давайте не на словах — покажу за 15–20 минут, как это выглядит именно под ваш формат: календарь, запись через интернет, напоминания. Вы просто оцените, подходит или нет. Когда удобнее: завтра до обеда или после? Или во вторник / в среду?</t>
+          <t>Давайте я вам просто покажу, как это выглядит. За 15–20 минут пройдёмся по календарю, записи и напоминаниям — уже на вашем формате. Когда удобнее: завтра до обеда или после? Или во вторник / в среду?</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Всегда даём выбор из двух вариантов времени. Не спрашиваем «вам интересно?» — спрашиваем «когда удобно»</t>
+          <t>Даём выбор из двух вариантов. Не спрашиваем «интересно ли» — спрашиваем «когда удобно»</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr"/>
     </row>
-    <row r="30" ht="76" customHeight="1">
+    <row r="30" ht="60" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
           <t>Если говорит «надо подумать»</t>
@@ -1150,7 +1144,7 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Конечно. Как раз поэтому и предлагаю короткий показ — без оплаты и без обязательств, просто посмотрите, как устроена система. После показа будет понятнее, есть ли о чём думать. Давайте поставим 15 минут на [день] — и вы спокойно примете решение?</t>
+          <t>Понимаю. Как раз поэтому и предлагаю короткую демонстрацию — посмотрите глазами, и уже после будет понятнее, есть ли о чём думать. Давайте поставим 15 минут на [день]?</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr"/>
@@ -1159,7 +1153,7 @@
     <row r="31" ht="76" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Закрепить договорённость</t>
+          <t>Закрепляем договорённость</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -1169,20 +1163,20 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Отлично. На какую почту или в какой мессенджер отправить ссылку и напоминание? Подтвердим: [дата], [время], показ «Блиц-запись», около 15–20 минут. Я за день и за час напомню. Хорошего дня, [Имя Отчество]!</t>
+          <t>Хорошо. Куда удобнее отправить ссылку — на почту или в мессенджер? Тогда подтверждаем: [дата], [время], демонстрация «Блиц-запись», минут 15–20. Я за день и за час напомню. Хорошего дня, [Имя Отчество]!</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>После звонка: письмо со ссылкой и задача в системе учёта клиентов (см. регламент после записи на показ)</t>
+          <t>После звонка: письмо со ссылкой + задача в CRM (см. регламент после записи на демонстрацию)</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr"/>
     </row>
-    <row r="32" ht="60" customHeight="1">
+    <row r="32" ht="76" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>7. Если показ сейчас не ставят</t>
+          <t>6. Если демонстрацию сейчас не ставят</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -1192,7 +1186,7 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Хорошо, не давлю. Тогда зафиксирую ваш запрос: [боль]. Могу направить короткое коммерческое предложение на почту и созвониться [день / время] — сравним с тем, как у вас сейчас. Какая почта удобнее?</t>
+          <t>Хорошо, настаивать не буду. Зафиксирую, что для вас важно: [боль]. Могу скинуть короткое коммерческое предложение на почту и созвониться [день / время] — сравним с тем, как у вас сейчас. Какая почта удобнее?</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1202,10 +1196,10 @@
       </c>
       <c r="E32" s="4" t="inlineStr"/>
     </row>
-    <row r="34" ht="188" customHeight="1">
+    <row r="34" ht="172" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>ПАМЯТКА МЕНЕДЖЕРУ: не продавать тариф в холодном звонке; не спорить с «Юклиентс» и «Дикиди» — звать сравнить на показе; не говорить дольше 40–50 секунд подряд; после каждого блока вопросов — пауза и слушание; цифры тарифа — только если клиент спросил сам (см. лист «Памятка по продукту»).</t>
+          <t>На заметку: тариф в холодном звонке не продаём; с «Юклиентс» и «Дикиди» не спорим — зовём сравнить на демонстрации; дольше 40–50 секунд подряд не говорим; после вопросов — пауза и слушаем; цену называем только если спросили (см. лист «Памятка по продукту»).</t>
         </is>
       </c>
     </row>
@@ -1229,14 +1223,14 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="88" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ОТРАБОТКА ВОЗРАЖЕНИЙ — «БЛИЦ-ЗАПИСЬ» (микро- и малый бизнес, индивидуальные предприниматели: салоны, автомойки, курсы, студии)</t>
+          <t>ОТРАБОТКА ВОЗРАЖЕНИЙ — «БЛИЦ-ЗАПИСЬ» (микро- и малый бизнес, ИП: салоны, автомойки, курсы, студии)</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -1250,12 +1244,12 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>Отработка (говорить)</t>
+          <t>Что говорим</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>Цель отработки</t>
+          <t>Зачем</t>
         </is>
       </c>
     </row>
@@ -1267,29 +1261,29 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Понимаю, поэтому и не отнимаю много времени. Предлагаю 15 минут показа в удобное время — вы просто посмотрите, есть ли смысл возвращаться к теме. Когда спокойнее: утро или вечер?</t>
+          <t>Понимаю, не буду вас долго держать. Предлагаю 15 минут демонстрации в удобное время — просто посмотрите, есть ли смысл вообще к этому возвращаться. Когда спокойнее: утром или вечером?</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Договориться о конкретном времени показа</t>
+          <t>Договориться о времени демонстрации</t>
         </is>
       </c>
     </row>
     <row r="4" ht="76" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Нас всё устраивает / и так нормально</t>
+          <t>Нас всё устраивает</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Отлично, значит процесс уже выстроен — это сильная сторона. Часто смотрят «Блиц» не потому что «всё плохо», а чтобы убрать лишние звонки администратору и не терять записи вечером и в выходные. Давайте за 15 минут сравните с тем, как у вас сейчас — вдруг окажется полезным запасным вариантом?</t>
+          <t>Хорошо, значит у вас уже порядок — это плюс. Часто к нам смотрят не потому, что «всё плохо», а чтобы администратор меньше сидел на телефоне и записи вечером не терялись. Давайте за 15 минут сравните с тем, как у вас сейчас — вдруг пригодится.</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Снять защиту «нас всё устраивает» и вызвать интерес</t>
+          <t>Снять «нас всё устраивает» и вызвать интерес</t>
         </is>
       </c>
     </row>
@@ -1301,16 +1295,16 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Значит, ценность записи через интернет вы уже понимаете — это хорошо. Клиенты часто приходят к нам из‑за цены «за мастера», перегруженного экрана или слабой поддержки под их задачи. Салон «Луна» и мойка «Элис» как раз переехали с «Юклиентс»: базу перенесли мы, плюс до шести месяцев в подарок за переход. Предлагаю коротко показать разницу — без обязательств.</t>
+          <t>Значит, с записью через интернет вы уже работаете — отлично. К нам часто приходят из‑за цены «за мастера», тяжёлого интерфейса или когда поддержка не слышит. Салон «Луна» и мойка «Элис» как раз переехали с «Юклиентс»: базу перенесли мы, плюс до шести месяцев в подарок. Могу коротко показать разницу на демонстрации.</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Не уговаривать «бросить» сервис, а предложить сравнить</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="92" customHeight="1">
+          <t>Не уговаривать бросить сервис — предложить сравнить</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="76" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Это дорого</t>
@@ -1318,63 +1312,63 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Давайте опираться на цифры. Ориентир — от 1 500 рублей в месяц при оплате на два года, при оплате на год — около 1 900 рублей в месяц; цена не растёт от числа мастеров. Для сравнения: салон «Луна» экономит порядка 13 500 рублей в год относительно прежнего сервиса. На показе посчитаем относительно вашей текущей схемы — часто выходит дешевле привычного.</t>
+          <t>Давайте по цифрам. Ориентир — от 1 500 рублей в месяц при оплате на два года, на год — около 1 900; от числа мастеров цена не растёт. Салон «Луна», например, экономит порядка 13 500 рублей в год относительно прошлого сервиса. На демонстрации прикинем под вашу схему — часто выходит дешевле привычного.</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Перевести разговор из эмоции в сравнение на показе</t>
+          <t>Увести от эмоции к сравнению на демонстрации</t>
         </is>
       </c>
     </row>
     <row r="7" ht="76" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>У нас маленький бизнес / я один (индивидуальный предприниматель, 1–2 мастера)</t>
+          <t>У нас маленький бизнес / я один</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Как раз для небольшого бизнеса сервис и делали простым: запись, календарь, база, напоминания — без лишних блоков «для сетей». Есть вариант с оплатой по факту записей через интернет (баланс от 1 000 рублей) — удобно, если поток небольшой. На показе покажем именно простой сценарий под вас.</t>
+          <t>Как раз для небольшого бизнеса и делали: запись, календарь, база, напоминания — без лишнего «для сетей». Если поток небольшой, есть оплата по факту записей через интернет, баланс от 1 000 рублей. На демонстрации покажем простой сценарий именно под вас.</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Убрать страх «это только для крупных»</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="92" customHeight="1">
+          <t>Убрать страх «это для крупных»</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="76" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Клиенты всё равно звонят / не будут пользоваться записью через интернет</t>
+          <t>Клиенты всё равно звонят</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Часть клиентов всегда будет звонить — и это нормально. Задача сервиса — забрать тех, кто готов записаться сам (вечером, с работы, из социальной сети), и разгрузить администратора. По практике больше 40% записей может приходить через интернет. Запись через администратора при этом никуда не девается.</t>
+          <t>Часть клиентов всегда будет звонить — это нормально. Сервис забирает тех, кто готов записаться сам: вечером, с работы, из соцсети. По практике больше 40% записей может приходить через интернет. Администратор при этом тоже может записывать, как раньше.</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Показать, что оба способа записи работают вместе</t>
+          <t>Показать, что оба способа работают вместе</t>
         </is>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Боимся переносить базу / потерять клиентов</t>
+          <t>Боимся переносить базу</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Переход берём на себя: в примерах внедрения переносили тысячи контактов и услуги целиком, бизнес не останавливали. Пробный период есть — сначала смотрите и проверяете, оплату принимаете, когда готовы.</t>
+          <t>Перенос берём на себя. В наших внедрениях переносили тысячи контактов и услуги, работа при этом не останавливалась. Сначала смотрите в тестовом доступе, платите, когда будете готовы.</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Снять страх переноса данных</t>
+          <t>Снять страх потери данных</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1380,12 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Мы подключаем и настраиваем услуги, расписание, сотрудников и ссылки на запись сами. Вам не нужно разбираться «с нуля». На показе как раз увидите, сколько действий займёт день администратора — обычно это проще тетради и переписки в чатах.</t>
+          <t>Мы сами подключаем и настраиваем: услуги, расписание, сотрудников, ссылки на запись. Вам не нужно разбираться с нуля. На демонстрации увидите, как выглядит обычный день администратора — обычно это проще тетради и переписки в чатах.</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Показать, что сопровождение берёт на себя «Форус»</t>
+          <t>Показать, что мы сопровождаем запуск</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1397,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Конечно, направлю короткое коммерческое предложение. Чтобы материал был в точку, уточню один момент: что сейчас больнее — пропущенные заявки, неявки или цена текущего сервиса? … Спасибо. И давайте сразу поставим 15 минут на просмотр — так предложение не потеряется в почте. Когда удобно?</t>
+          <t>Конечно, направлю. Чтобы не слать лишнее, уточню: что сейчас больше всего мешает — пропущенные заявки, неявки или цена текущего сервиса? … Спасибо. И давайте сразу поставим 15 минут — так материал не потеряется в почте. Когда удобно?</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Не оставлять разговор только на «пришлите»</t>
+          <t>Не оставлять только на «пришлите»</t>
         </is>
       </c>
     </row>
@@ -1420,63 +1414,63 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Логично. Давайте пригласим его или её сразу на показ — за те же 15–20 минут оба увидите систему и быстрее примете решение. Когда вам обоим удобно?</t>
+          <t>Логично. Давайте сразу пригласим его или её на демонстрацию — за те же 15–20 минут оба посмотрите и быстрее решите. Когда вам двоим удобно?</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Пригласить на показ и руководителя, и того, кто влияет на решение</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="92" customHeight="1">
+          <t>Пригласить на демонстрацию ЛПР и того, кто влияет</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="76" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Работаем в тетради / таблице — нам хватает</t>
+          <t>Работаем в тетради / таблице</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Тетрадь понятна и привычна. Обычно ломается в час пик: накладки, потерянные сообщения в мессенджере, нет напоминаний. «Блиц» не усложняет жизнь — это тот же журнал, только в цифровом виде, плюс запись через интернет и напоминания. Посмотрите 15 минут — если тетрадь реально удобнее, честно останетесь на ней.</t>
+          <t>Тетрадь понятная, спорить не буду. Обычно она ломается в час пик: накладки, потерянные сообщения, нет напоминаний. «Блиц» — тот же журнал, только в телефоне и на компьютере, плюс запись через интернет. Посмотрите 15 минут — если тетрадь удобнее, так и останетесь.</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Уважение к привычке и приглашение на показ</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="60" customHeight="1">
+          <t>Уважить привычку и пригласить на демонстрацию</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Нет сайта — запись через интернет не нужна</t>
+          <t>Нет сайта — нам это не нужно</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Сайт не обязателен. Ссылку на запись ставят в мессенджер, социальные сети, на карты — клиент переходит по ссылке и выбирает время. Многие индивидуальные предприниматели начинают именно так.</t>
+          <t>Сайт не обязателен. Ссылку на запись ставят в мессенджер, соцсети, на карты — клиент переходит и выбирает время. Многие ИП так и начинают.</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Убрать ложный барьер «нужен сайт»</t>
+          <t>Убрать барьер «нужен сайт»</t>
         </is>
       </c>
     </row>
     <row r="15" ht="76" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Не доверяем новым сервисам / кто вы такие</t>
+          <t>Кто вы такие / не доверяем</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>«Блиц-запись» — разработка группы компаний «Форус»: более 30 лет на рынке, официальный партнёр фирмы «1С», продукт в реестре российского программного обеспечения. Рядом поддержка и помощь при запуске, не «коробка без ответа». На показе покажем живой кабинет и примеры таких же салонов и моек.</t>
+          <t>Мы из группы компаний «Форус» — больше 30 лет на рынке, официальный партнёр фирмы «1С». «Блиц-запись» — наша разработка, сервис в реестре российского программного обеспечения. Рядом живая поддержка, не бросаем после оплаты. На демонстрации покажем кабинет и примеры салонов и моек.</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Укрепить доверие к «Форус»</t>
+          <t>Укрепить доверие</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1482,12 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Как раз вне пика удобнее спокойно настроить запись и базу, чтобы к сезону уже принимать заявки круглосуточно. Давайте поставим короткое время на этой неделе — потом будет сложнее выкроить время.</t>
+          <t>Как раз между сезонами удобнее спокойно всё настроить, чтобы к пику уже принимать заявки круглосуточно. Давайте найдём короткое окно на этой неделе — потом времени будет ещё меньше.</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Создать срочность через подготовку к сезону</t>
+          <t>Связать с подготовкой к сезону</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1499,12 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Ориентир: 2 500 рублей в месяц при коротком сроке; при оплате на год — около 1 900 рублей в месяц, на два года — от 1 500 рублей в месяц. Точную схему лучше показать на встрече вместе с вашим сценарием: сколько сотрудников, есть ли уже сервис. Могу забронировать 15 минут — и сразу посчитаем.</t>
+          <t>Ориентир такой: 2 500 рублей в месяц при коротком сроке; на год — около 1 900; на два года — от 1 500. Точнее посчитаем на демонстрации под ваш сценарий: сколько людей работает, есть ли уже сервис. Могу забронировать 15 минут — и сразу прикинем.</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>От цены — к показу, без торга в холодном звонке</t>
+          <t>От цены — к демонстрации</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1532,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ПАМЯТКА МЕНЕДЖЕРУ — «БЛИЦ-ЗАПИСЬ» (для подготовки к звонку; клиенту не читать целиком)</t>
+          <t>ПАМЯТКА МЕНЕДЖЕРУ — «БЛИЦ-ЗАПИСЬ» (себе перед звонком; клиенту не читать)</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -1555,7 +1549,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1">
+    <row r="3" ht="44" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Продукт</t>
@@ -1563,11 +1557,11 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>«Блиц-запись» — сервис для управления записями клиентов, расписанием, клиентской базой и загрузкой сотрудников в одном рабочем пространстве. Разработка научно-производственной фирмы «Форус».</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="60" customHeight="1">
+          <t>«Блиц-запись» — сервис для записи клиентов, расписания, клиентской базы и загрузки сотрудников в одном окне. Разработка научно-производственной фирмы «Форус».</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="44" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Для кого</t>
@@ -1575,7 +1569,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Салоны красоты и барбершопы; автомойки и мойки самообслуживания; медицинские и стоматологические клиники; образовательные центры и курсы; фитнес и спортивные студии; частные специалисты; любой бизнес по предварительной записи.</t>
+          <t>Салоны красоты и барбершопы; автомойки; клиники; курсы и учебные центры; фитнес и студии; частные специалисты; любой бизнес по предварительной записи.</t>
         </is>
       </c>
     </row>
@@ -1587,38 +1581,38 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Микро- и малый бизнес, индивидуальные предприниматели.</t>
+          <t>Микро- и малый бизнес, ИП.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Сильные стороны</t>
+          <t>Чем сильны</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Простая запись, расписание и база; цена не зависит от числа мастеров; сопровождение внедрения от «Форус»; переход с других сервисов целиком; до шести месяцев в подарок при переходе; реестр российского программного обеспечения.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="76" customHeight="1">
+          <t>Простая запись, расписание и база; цена не зависит от числа мастеров; помогаем внедрить; переход с других сервисов берём на себя; до шести месяцев в подарок при переходе; реестр российского программного обеспечения.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Основные возможности</t>
+          <t>Что умеет</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Запись через интернет круглосуточно; единое место администратора; управление загрузкой (сотрудники, кабинеты, посты); напоминания; клиентская база и история; анализ загрузки; роли и доступы; связь с телефонией, программой учёта клиентов, кассой, «1С», мессенджерами; доступ из браузера без установки программ.</t>
+          <t>Запись через интернет круглосуточно; календарь администратора; загрузка по сотрудникам, кабинетам, постам; напоминания; база и история; анализ загрузки; роли; связь с телефонией, CRM, кассой, «1С», мессенджерами; работает в браузере.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Цифры с сайта и коммерческого предложения</t>
+          <t>Цифры</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -1627,19 +1621,19 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="76" customHeight="1">
+    <row r="9" ht="60" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Тарифы (ориентир)</t>
+          <t>Тарифы</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>3 месяца — 2 500 рублей в месяц; 6 месяцев — 2 300 рублей в месяц; 1 год — 1 900 рублей в месяц; 2 года — 1 500 рублей в месяц. Есть вариант оплаты за фактические записи через интернет (баланс от 1 000 рублей). При переходе с другого сервиса — до шести месяцев дополнительно.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="44" customHeight="1">
+          <t>3 месяца — 2 500 ₽/мес; 6 месяцев — 2 300 ₽/мес; 1 год — 1 900 ₽/мес; 2 года — 1 500 ₽/мес. Есть оплата за фактические записи через интернет (баланс от 1 000 ₽). При переходе с другого сервиса — до шести месяцев дополнительно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Пробный период</t>
@@ -1647,35 +1641,35 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>14 дней бесплатно / тестовый доступ (озвучивать как возможность «потрогать» после показа).</t>
+          <t>14 дней бесплатно / тестовый доступ — обычно после демонстрации.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Цель холодного звонка</t>
+          <t>Цель звонка</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Записать клиента на показ сервиса на 15–20 минут (не продавать подписку в звонке).</t>
+          <t>Записать на демонстрацию 15–20 минут. Тариф в холодном звонке не продаём.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="44" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Контакты продукта</t>
+          <t>Контакты</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>+7 992 117-29-16 · vmoskvitina@forus.ru · blitz@forus.ru · сайт блиц-запись.рф · «Форус»: forus.ru, +7 (3952) 78-00-00</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1">
+          <t>+7 992 117-29-16 · vmoskvitina@forus.ru · blitz@forus.ru · блиц-запись.рф · «Форус»: forus.ru, +7 (3952) 78-00-00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="44" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Пример «Луна»</t>
@@ -1683,11 +1677,11 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Салон красоты, переход с «Юклиентс». Около 2000 клиентов, 6 мастеров, около 100 услуг. Экономия около 37% (с 36 360 до 22 800 рублей в год) плюс шесть месяцев в подарок. Оплата годовой подписки 07.08.2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="60" customHeight="1">
+          <t>Салон, переход с «Юклиентс». ~2000 клиентов, 6 мастеров, ~100 услуг. Экономия около 37% (36 360 → 22 800 ₽/год) + 6 месяцев в подарок. Год оплатили 07.08.2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Пример «Элис»</t>
@@ -1695,19 +1689,19 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Автомоечный комплекс, 8 постов, около 2000 записей в месяц. Переход с «Юклиентс». Под клиента: календарь, быстрая запись администратором, зарплаты, касса. Плюс шесть месяцев в подарок. Годовая подписка с апреля 2026.</t>
+          <t>Автомойка, 8 постов, ~2000 записей/мес. Переход с «Юклиентс». Календарь, быстрая запись, зарплаты, касса. +6 месяцев. Год с апреля 2026.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="44" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>После записи на показ</t>
+          <t>После записи на демонстрацию</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Письмо со ссылкой → напоминание за день → за час → менеджер на встрече → обратная связь в течение трёх дней (см. регламент в репозитории).</t>
+          <t>Письмо со ссылкой → напоминание за день → за час → менеджер на встрече → обратная связь в течение трёх дней.</t>
         </is>
       </c>
     </row>
@@ -1719,7 +1713,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Не читать весь функционал; не спорить с конкурентами; не давить тарифом; не заканчивать звонок без следующего шага; не говорить больше клиента.</t>
+          <t>Не читать весь функционал; не спорить с конкурентами; не давить ценой; не заканчивать без следующего шага; не говорить больше клиента.</t>
         </is>
       </c>
     </row>
@@ -1749,7 +1743,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ШПАРГАЛКА ПО ПРИМЕРАМ ВНЕДРЕНИЯ — коротко вставить в разговор</t>
+          <t>ПРИМЕРЫ ВНЕДРЕНИЯ — коротко вставить в разговор</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -1774,7 +1768,7 @@
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>Результат / фраза в звонке</t>
+          <t>Что сказать</t>
         </is>
       </c>
     </row>
@@ -1791,12 +1785,12 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>«Юклиентс» дорого (цена от числа мастеров), лишний функционал, медленная загрузка</t>
+          <t>«Юклиентс» дорого (цена от числа мастеров), лишний функционал, медленно грузится</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>«Перенесли две тысячи клиентов целиком, экономия около трети в год, плюс шесть месяцев за переход. Салон остался на годовой подписке.»</t>
+          <t>«Перенесли две тысячи клиентов, экономия около трети в год, плюс шесть месяцев за переход. Салон остался на годе.»</t>
         </is>
       </c>
     </row>
@@ -1813,7 +1807,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Дорого (около 120 тысяч рублей в год), ошибки в зарплатах, отказ конкурента по телефонии, тяжёлый интерфейс</t>
+          <t>Дорого (около 120 тысяч в год), ошибки в зарплатах, не подключили телефонию, тяжёлый интерфейс</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -1825,7 +1819,7 @@
     <row r="5" ht="44" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Как вставлять: 1) клиент назвал конкурента — пример перехода; 2) боится переноса данных — «перенос берём на себя»; 3) жалуется на цену — цифры «Луны»; 4) автобизнес и посты — «Элис». Одного примера за звонок достаточно.</t>
+          <t>Когда вставлять: назвал конкурента — пример перехода; боится переноса — «переносим сами»; жалуется на цену — цифры «Луны»; автобизнес — «Элис». Одного примера за звонок хватает.</t>
         </is>
       </c>
     </row>

--- a/Blitz-zapis-cold-call-script.xlsx
+++ b/Blitz-zapis-cold-call-script.xlsx
@@ -89,7 +89,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -111,11 +111,55 @@
         <color rgb="00D0D7DE"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D0D7DE"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D0D7DE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D7DE"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D0D7DE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D7DE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D0D7DE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D7DE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D7DE"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -135,6 +179,8 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -501,7 +547,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -516,10 +562,6 @@
           <t>СКРИПТ ХОЛОДНОГО ЗВОНКА: «БЛИЦ-ЗАПИСЬ»  |  Цель — записать клиента на демонстрацию сервиса (15–20 минут)</t>
         </is>
       </c>
-      <c r="B1" s="1" t="n"/>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
     </row>
     <row r="2" ht="204" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -527,6 +569,10 @@
           <t>Как идёт звонок (для себя, клиенту не читать): сначала знакомимся и коротко говорим, кто мы → задаём вопросы и слушаем → своими словами повторяем, что услышали → рассказываем только то, что откликнулось клиенту → если нужно, приводим пример → приглашаем на демонстрацию. В звонке не продаём тариф — договариваемся о встрече.</t>
         </is>
       </c>
+      <c r="B2" s="7" t="n"/>
+      <c r="C2" s="7" t="n"/>
+      <c r="D2" s="7" t="n"/>
+      <c r="E2" s="8" t="n"/>
     </row>
     <row r="3" ht="60" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -1202,6 +1248,10 @@
           <t>На заметку: тариф в холодном звонке не продаём; с «Юклиентс» и «Дикиди» не спорим — зовём сравнить на демонстрации; дольше 40–50 секунд подряд не говорим; после вопросов — пауза и слушаем; цену называем только если спросили (см. лист «Памятка по продукту»).</t>
         </is>
       </c>
+      <c r="B34" s="7" t="n"/>
+      <c r="C34" s="7" t="n"/>
+      <c r="D34" s="7" t="n"/>
+      <c r="E34" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1220,7 +1270,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="90" customWidth="1" min="2" max="2"/>
@@ -1233,8 +1283,6 @@
           <t>ОТРАБОТКА ВОЗРАЖЕНИЙ — «БЛИЦ-ЗАПИСЬ» (микро- и малый бизнес, ИП: салоны, автомойки, курсы, студии)</t>
         </is>
       </c>
-      <c r="B1" s="1" t="n"/>
-      <c r="C1" s="1" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
@@ -1523,7 +1571,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
@@ -1535,7 +1583,6 @@
           <t>ПАМЯТКА МЕНЕДЖЕРУ — «БЛИЦ-ЗАПИСЬ» (себе перед звонком; клиенту не читать)</t>
         </is>
       </c>
-      <c r="B1" s="1" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
@@ -1732,7 +1779,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
@@ -1746,9 +1793,6 @@
           <t>ПРИМЕРЫ ВНЕДРЕНИЯ — коротко вставить в разговор</t>
         </is>
       </c>
-      <c r="B1" s="1" t="n"/>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
@@ -1822,6 +1866,9 @@
           <t>Когда вставлять: назвал конкурента — пример перехода; боится переноса — «переносим сами»; жалуется на цену — цифры «Луны»; автобизнес — «Элис». Одного примера за звонок хватает.</t>
         </is>
       </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
